--- a/Descarga-Mis-Comprobantes.xlsx
+++ b/Descarga-Mis-Comprobantes.xlsx
@@ -49,13 +49,13 @@
     <t xml:space="preserve">Descarga Recibidos</t>
   </si>
   <si>
-    <t xml:space="preserve">Ubicación Emitidos</t>
+    <t xml:space="preserve">Ubicacion Emitidos</t>
   </si>
   <si>
     <t xml:space="preserve">Nombre Emitidos</t>
   </si>
   <si>
-    <t xml:space="preserve">Ubicación Recibidos</t>
+    <t xml:space="preserve">Ubicacion Recibidos</t>
   </si>
   <si>
     <t xml:space="preserve">Nombre Recibidos</t>
